--- a/data/hardtail/Tumbleweed Prospector 2025.xlsx
+++ b/data/hardtail/Tumbleweed Prospector 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E6FB8B-3E0E-9C4B-B6B2-9BC055DF9C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6AD81C-5176-EF45-A185-57D96BC0A628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -1330,9 +1330,6 @@
       <c r="A39" t="s">
         <v>34</v>
       </c>
-      <c r="B39" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">

--- a/data/hardtail/Tumbleweed Prospector 2025.xlsx
+++ b/data/hardtail/Tumbleweed Prospector 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6AD81C-5176-EF45-A185-57D96BC0A628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A6F46F-1838-4D41-ADF5-16F7B1B5A567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1350,8 +1350,7 @@
         <v>38</v>
       </c>
       <c r="B42">
-        <f>3.8*25.4</f>
-        <v>96.52</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="43" spans="1:7">
